--- a/AAII_Financials/Quarterly/PSN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PSN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="92">
   <si>
     <t>PSN</t>
   </si>
@@ -656,480 +656,493 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43371</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43280</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43189</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43098</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1575900</v>
+      </c>
+      <c r="E8" s="3">
         <v>1491200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1603800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1621700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1584300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1554400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1734300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1810100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1670500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1535700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1494200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1418600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1356500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1173500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1103100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1134400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1008700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>949100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>950700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>956100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>879400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>874700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>964300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1004200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>979500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>971000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1037400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1023300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>989700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>904400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>928900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>976200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>845600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>754700</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>816500</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1280600</v>
+      </c>
+      <c r="E9" s="3">
         <v>1133800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1234500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1261900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1236000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1200400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1364600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1449800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1318900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1210800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1127000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1124300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1068200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>917200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>860500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>872400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>781800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>733900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>723900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>734700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>680300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>669100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>734400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>788800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>749300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>769600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>825600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>798600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>784700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>714200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>740800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>783000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>668200</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>603000</v>
       </c>
-      <c r="AK9" s="3" t="s">
+      <c r="AL9" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>295200</v>
+      </c>
+      <c r="E10" s="3">
         <v>357400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>369300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>359900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>348400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>354000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>369800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>360300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>351500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>324800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>367200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>294300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>288300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>256300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>242600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>262000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>226900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>215200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>226800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>221400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>199100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>205600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>229900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>215400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>230200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>201400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>211900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>224700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>205000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>190200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>188100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>193200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>177400</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>151700</v>
       </c>
-      <c r="AK10" s="3" t="s">
+      <c r="AL10" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1167,8 +1180,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1274,8 +1288,11 @@
       <c r="AK12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1381,58 +1398,61 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3">
         <v>5100</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G14" s="3">
-        <v>2600</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>5</v>
+      <c r="F14" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
       </c>
       <c r="J14" s="3">
+        <v>22900</v>
+      </c>
+      <c r="K14" s="3">
         <v>2500</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M14" s="3">
         <v>20400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-5100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>5500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1900</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>5</v>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -1443,17 +1463,17 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>5</v>
+      <c r="W14" s="3">
+        <v>0</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>5</v>
+      <c r="Y14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>5</v>
@@ -1461,80 +1481,83 @@
       <c r="AB14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AC14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD14" s="3">
         <v>100</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>5300</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>800</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>4100</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
       <c r="AH14" s="3">
         <v>0</v>
       </c>
       <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>-132000</v>
-      </c>
-      <c r="AJ14" s="3">
-        <v>2300</v>
       </c>
       <c r="AK14" s="3">
         <v>2300</v>
       </c>
+      <c r="AL14" s="3">
+        <v>2300</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>35400</v>
+      </c>
+      <c r="E15" s="3">
         <v>34800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>29500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>28700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>27400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>26300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>24700</v>
-      </c>
-      <c r="J15" s="3">
-        <v>23600</v>
       </c>
       <c r="K15" s="3">
         <v>23600</v>
       </c>
       <c r="L15" s="3">
+        <v>23600</v>
+      </c>
+      <c r="M15" s="3">
         <v>23800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>34700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>29400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>28000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>27800</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1595,8 +1618,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1631,222 +1657,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1540800</v>
+      </c>
+      <c r="E17" s="3">
         <v>1396700</v>
       </c>
-      <c r="E17" s="3">
-        <v>1494200</v>
-      </c>
       <c r="F17" s="3">
+        <v>1493700</v>
+      </c>
+      <c r="G17" s="3">
         <v>1522100</v>
       </c>
-      <c r="G17" s="3">
-        <v>1485400</v>
-      </c>
       <c r="H17" s="3">
+        <v>1488000</v>
+      </c>
+      <c r="I17" s="3">
         <v>1444400</v>
       </c>
-      <c r="I17" s="3">
-        <v>1629200</v>
-      </c>
       <c r="J17" s="3">
+        <v>1625000</v>
+      </c>
+      <c r="K17" s="3">
         <v>1693500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1542200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1431800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1369900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1340000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1278200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1116500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1049800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1070400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>976100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>913400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>903800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>916300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>859100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>849100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>922700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>938000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>933200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>947300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1013100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>969800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>998400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>881400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>904800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>921000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>681800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>718100</v>
       </c>
-      <c r="AK17" s="3" t="s">
+      <c r="AL17" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>35000</v>
+      </c>
+      <c r="E18" s="3">
         <v>94500</v>
       </c>
-      <c r="E18" s="3">
-        <v>109600</v>
-      </c>
       <c r="F18" s="3">
+        <v>110100</v>
+      </c>
+      <c r="G18" s="3">
         <v>99700</v>
       </c>
-      <c r="G18" s="3">
-        <v>98900</v>
-      </c>
       <c r="H18" s="3">
+        <v>96300</v>
+      </c>
+      <c r="I18" s="3">
         <v>109900</v>
       </c>
-      <c r="I18" s="3">
-        <v>105100</v>
-      </c>
       <c r="J18" s="3">
+        <v>109300</v>
+      </c>
+      <c r="K18" s="3">
         <v>116600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>128300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>103900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>124300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>78600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>78300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>57000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>53300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>64000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>32600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>35700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>46900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>39800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>20300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>25600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>41600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>66200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>46300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>23700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>24300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>53500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-8700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>23000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>24100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>55200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>163800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>36600</v>
       </c>
-      <c r="AK18" s="3" t="s">
+      <c r="AL18" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1884,245 +1917,252 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-6100</v>
       </c>
-      <c r="E20" s="3">
-        <v>3700</v>
-      </c>
       <c r="F20" s="3">
+        <v>3300</v>
+      </c>
+      <c r="G20" s="3">
         <v>-9800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-4400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1000</v>
       </c>
-      <c r="I20" s="3">
-        <v>6700</v>
-      </c>
       <c r="J20" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="K20" s="3">
         <v>-2800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>15900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>3400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>48700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-10100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>4500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>3400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>2100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-2700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>1800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>1000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>1900</v>
       </c>
-      <c r="AK20" s="3" t="s">
+      <c r="AL20" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>135400</v>
+        <v>55000</v>
       </c>
       <c r="E21" s="3">
         <v>135400</v>
       </c>
       <c r="F21" s="3">
+        <v>136400</v>
+      </c>
+      <c r="G21" s="3">
         <v>138200</v>
       </c>
-      <c r="G21" s="3">
-        <v>130700</v>
-      </c>
       <c r="H21" s="3">
+        <v>128100</v>
+      </c>
+      <c r="I21" s="3">
         <v>137200</v>
       </c>
-      <c r="I21" s="3">
-        <v>123100</v>
-      </c>
       <c r="J21" s="3">
+        <v>146100</v>
+      </c>
+      <c r="K21" s="3">
         <v>143000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>135900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>124300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>110300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>118100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>106900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>80300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>86600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>93300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>63600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>66400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>83300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>77200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>55400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>58600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>76200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>99000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>79300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>55900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>56600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>81800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>24100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>54200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>45700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>79800</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>177600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>47500</v>
       </c>
-      <c r="AK21" s="3" t="s">
+      <c r="AL21" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E22" s="3">
         <v>16000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>13000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>13500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>12600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>12200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>12500</v>
-      </c>
-      <c r="J22" s="3">
-        <v>13000</v>
       </c>
       <c r="K22" s="3">
         <v>13000</v>
@@ -2131,296 +2171,305 @@
         <v>13000</v>
       </c>
       <c r="M22" s="3">
+        <v>13000</v>
+      </c>
+      <c r="N22" s="3">
         <v>9100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>8600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>7300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>6500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>8400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>6300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>4500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>3900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>4200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>4100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>4900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>4500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>7300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>5500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>4200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>4000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>4200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>4900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>6400</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>8300</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>6400</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>5900</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>4500</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>4000</v>
       </c>
-      <c r="AK22" s="3" t="s">
+      <c r="AL22" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E23" s="3">
         <v>81300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>94700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>97800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>89200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>100800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>88100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>108100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>103100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>68300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>72300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>75000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>70000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>46800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>48400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>57400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>28500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>32000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>41400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>35900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>15900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>19400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>36400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>62500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>43000</v>
-      </c>
-      <c r="AB23" s="3">
-        <v>19500</v>
       </c>
       <c r="AC23" s="3">
         <v>19500</v>
       </c>
       <c r="AD23" s="3">
+        <v>19500</v>
+      </c>
+      <c r="AE23" s="3">
         <v>45800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-13400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>15300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>16100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>50200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>159100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>34500</v>
       </c>
-      <c r="AK23" s="3" t="s">
+      <c r="AL23" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E24" s="3">
         <v>16100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>19900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>16000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>18700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>19000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>18700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>22500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>22400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>13300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>14200</v>
-      </c>
-      <c r="N24" s="3">
-        <v>15200</v>
       </c>
       <c r="O24" s="3">
         <v>15200</v>
       </c>
       <c r="P24" s="3">
+        <v>15200</v>
+      </c>
+      <c r="Q24" s="3">
         <v>11500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>12000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>13800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>5700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>8100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>5300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>9200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>3800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>5400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>9500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>16000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>11900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>5100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-15500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-53500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>4200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>9000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>5400</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2526,222 +2575,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E26" s="3">
         <v>65200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>74800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>81800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>70500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>81800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>69400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>85600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>80700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>55000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>58100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>59800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>54800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>35300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>36300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>43600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>22800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>23800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>36100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>26800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>12000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>14000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>26900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>46500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>31100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>14400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>22300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>61300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>40100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>13400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>14200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>46100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>150000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>29100</v>
       </c>
-      <c r="AK26" s="3" t="s">
+      <c r="AL26" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="E27" s="3">
         <v>52900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>55600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>64100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>55200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>66200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>54200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>72000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>69200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>39800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>44900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>47400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>43200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>25600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>28100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>29600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>18300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>20700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>29000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>19400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>6700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>9000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>21600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>40700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>23300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>13000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>13700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>56800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>40300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>9700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>7400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>41200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>148400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>25300</v>
       </c>
-      <c r="AK27" s="3" t="s">
+      <c r="AL27" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2847,8 +2905,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2954,8 +3015,11 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3061,8 +3125,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3168,222 +3235,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-15500</v>
+      </c>
+      <c r="E32" s="3">
         <v>6100</v>
       </c>
-      <c r="E32" s="3">
-        <v>-3700</v>
-      </c>
       <c r="F32" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="G32" s="3">
         <v>9800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>4400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1000</v>
       </c>
-      <c r="I32" s="3">
-        <v>-6700</v>
-      </c>
       <c r="J32" s="3">
+        <v>12000</v>
+      </c>
+      <c r="K32" s="3">
         <v>2800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-15900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-3400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-48700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>10100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-3400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>2700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>1600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-1900</v>
       </c>
-      <c r="AK32" s="3" t="s">
+      <c r="AL32" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="E33" s="3">
         <v>52900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>55600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>64100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>55200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>66200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>54200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>72000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>69200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>39800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>44900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>47400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>43200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>25600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>28100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>29600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>18300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>20700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>29000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>19400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>6700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>9000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>21600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>40700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>23300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>13000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>13700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>56800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>40300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>9700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>7400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>41200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>148400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>25300</v>
       </c>
-      <c r="AK33" s="3" t="s">
+      <c r="AL33" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3489,227 +3565,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="E35" s="3">
         <v>52900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>55600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>64100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>55200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>66200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>54200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>72000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>69200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>39800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>44900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>47400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>43200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>25600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>28100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>29600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>18300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>20700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>29000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>19400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>6700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>9000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>21600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>40700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>23300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>13000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>13700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>56800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>40300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>9700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>7400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>41200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>148400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>25300</v>
       </c>
-      <c r="AK35" s="3" t="s">
+      <c r="AL35" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43371</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43280</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43189</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43098</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3747,8 +3832,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3786,101 +3872,102 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>266000</v>
+      </c>
+      <c r="E41" s="3">
         <v>283900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>466400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>422600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>411300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>269700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>453500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>558800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>528500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>423100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>272900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>205400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>178600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>220400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>262500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>147500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>126000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>285600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>342600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>275500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>483400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>398200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>483600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>614000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>129600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>119300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>182700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>133900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>202900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>121400</v>
       </c>
-      <c r="AG41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH41" s="3" t="s">
         <v>5</v>
       </c>
@@ -3893,8 +3980,11 @@
       <c r="AK41" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL41" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4000,101 +4090,104 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2208500</v>
+      </c>
+      <c r="E43" s="3">
         <v>2118400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2040200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2046400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2004200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1947700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1841900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1825000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1846600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1791500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1673200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1663400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1661900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1447400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1351400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1353000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1336800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1246200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1177500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1196700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1206200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1301300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1275100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1386000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1362900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1384700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1246600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1257300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1310700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1223700</v>
       </c>
-      <c r="AG43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH43" s="3" t="s">
         <v>5</v>
       </c>
@@ -4107,8 +4200,11 @@
       <c r="AK43" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL43" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4151,8 +4247,8 @@
       <c r="P44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4214,13 +4310,16 @@
       <c r="AK44" s="3">
         <v>0</v>
       </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>5</v>
+      <c r="D45" s="3">
+        <v>17200</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>5</v>
@@ -4258,57 +4357,57 @@
       <c r="P45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R45" s="3">
         <v>105900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>110300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>120800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>109100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>112200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>114300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>104700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>102800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>84400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>81600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>96700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>97900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>97100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>83000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>82400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>86100</v>
       </c>
-      <c r="AG45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH45" s="3" t="s">
         <v>5</v>
       </c>
@@ -4321,101 +4420,104 @@
       <c r="AK45" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL45" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2720300</v>
+      </c>
+      <c r="E46" s="3">
         <v>2594100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2683500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2649000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2593900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2401200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2462400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2554700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2573700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2427300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2137500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2015500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1980200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1801300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1719800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1610800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1583600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1641000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1632400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1586600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1794400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1802200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1843100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2081600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1589200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1602000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1526400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1474300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1596000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1431200</v>
       </c>
-      <c r="AG46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH46" s="3" t="s">
         <v>5</v>
       </c>
@@ -4428,101 +4530,104 @@
       <c r="AK46" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL46" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>153300</v>
+      </c>
+      <c r="E47" s="3">
         <v>162300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>148600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>156400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>150700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>142200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>138800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>194500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>157200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>145000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>128200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>164900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>118900</v>
-      </c>
-      <c r="P47" s="3">
-        <v>107400</v>
       </c>
       <c r="Q47" s="3">
         <v>107400</v>
       </c>
       <c r="R47" s="3">
+        <v>107400</v>
+      </c>
+      <c r="S47" s="3">
         <v>99400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>115500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>114200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>110700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>102700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>86000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>76000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>69000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>71300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>64900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>65700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>68600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>66600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>73500</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>67200</v>
       </c>
-      <c r="AG47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH47" s="3" t="s">
         <v>5</v>
       </c>
@@ -4535,101 +4640,104 @@
       <c r="AK47" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL47" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>317700</v>
+      </c>
+      <c r="E48" s="3">
         <v>314800</v>
       </c>
-      <c r="E48" s="3">
-        <v>277800</v>
-      </c>
       <c r="F48" s="3">
+        <v>286800</v>
+      </c>
+      <c r="G48" s="3">
         <v>268900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>272800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>280600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>274500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>245900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>243100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>252800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>265900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>264300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>268300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>247500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>255100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>259900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>269900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>273700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>291300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>297900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>308500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>323300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>334800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>336800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>351700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>358000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>358500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>329800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>314800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>315100</v>
       </c>
-      <c r="AG48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH48" s="3" t="s">
         <v>5</v>
       </c>
@@ -4642,101 +4750,104 @@
       <c r="AK48" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL48" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2805600</v>
+      </c>
+      <c r="E49" s="3">
         <v>2831400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2512500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2502900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2523200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2446700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2432600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2239100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2039000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2053300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2068200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2079400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1933000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1898000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1916000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1934500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1956800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1601600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1620500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1647400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1461000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1483600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1507900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1240500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1260300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1281000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1307300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1331200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1152000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1172000</v>
       </c>
-      <c r="AG49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH49" s="3" t="s">
         <v>5</v>
       </c>
@@ -4749,8 +4860,11 @@
       <c r="AK49" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL49" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4856,8 +4970,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4963,101 +5080,104 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>49000</v>
+      </c>
+      <c r="E52" s="3">
         <v>49200</v>
       </c>
-      <c r="E52" s="3">
-        <v>58800</v>
-      </c>
       <c r="F52" s="3">
+        <v>49800</v>
+      </c>
+      <c r="G52" s="3">
         <v>52500</v>
-      </c>
-      <c r="G52" s="3">
-        <v>46400</v>
       </c>
       <c r="H52" s="3">
         <v>46400</v>
       </c>
       <c r="I52" s="3">
+        <v>46400</v>
+      </c>
+      <c r="J52" s="3">
         <v>46200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>45700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>63000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>62500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>64000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>60300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>62300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>61100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>199900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>190300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>184000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>178400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>176100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>189400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>189300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>179900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>182900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>188500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>185100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>181900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>189500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>160800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>119200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>47500</v>
       </c>
-      <c r="AG52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH52" s="3" t="s">
         <v>5</v>
       </c>
@@ -5070,8 +5190,11 @@
       <c r="AK52" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL52" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5177,101 +5300,104 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6106900</v>
+      </c>
+      <c r="E54" s="3">
         <v>6012100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5769500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5736700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5721200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5449100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5488000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5443300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5238700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5098400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4804100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4733000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4507500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4255800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4198100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4095000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>4109800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3808800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3830900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>3823900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>3839300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>3865000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>3937700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>3918800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>3451200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>3488600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>3450400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>3362600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>3255500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>3033000</v>
       </c>
-      <c r="AG54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH54" s="3" t="s">
         <v>5</v>
       </c>
@@ -5284,8 +5410,11 @@
       <c r="AK54" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL54" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5323,8 +5452,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5362,101 +5492,102 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>246900</v>
+      </c>
+      <c r="E57" s="3">
         <v>232600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>250500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>271400</v>
-      </c>
-      <c r="G57" s="3">
-        <v>288500</v>
       </c>
       <c r="H57" s="3">
         <v>288500</v>
       </c>
       <c r="I57" s="3">
+        <v>288500</v>
+      </c>
+      <c r="J57" s="3">
         <v>207600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>300200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>252800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>274100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>242800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>266300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>237200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>209500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>201400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>200800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>194700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>157100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>196300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>188800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>191700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>219200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>225700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>208300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>209900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>235400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>216600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>226600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>227700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>203700</v>
       </c>
-      <c r="AG57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH57" s="3" t="s">
         <v>5</v>
       </c>
@@ -5469,52 +5600,55 @@
       <c r="AK57" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL57" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>44900</v>
+      </c>
+      <c r="E58" s="3">
         <v>46900</v>
       </c>
-      <c r="E58" s="3">
-        <v>45400</v>
-      </c>
       <c r="F58" s="3">
+        <v>49500</v>
+      </c>
+      <c r="G58" s="3">
         <v>53600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>141700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>492000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>519800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>170800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>56000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>58000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>61200</v>
-      </c>
-      <c r="N58" s="3">
-        <v>59300</v>
       </c>
       <c r="O58" s="3">
         <v>59300</v>
       </c>
       <c r="P58" s="3">
+        <v>59300</v>
+      </c>
+      <c r="Q58" s="3">
         <v>57500</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>1700</v>
       </c>
       <c r="R58" s="3">
         <v>1700</v>
@@ -5526,44 +5660,44 @@
         <v>1700</v>
       </c>
       <c r="U58" s="3">
+        <v>1700</v>
+      </c>
+      <c r="V58" s="3">
         <v>1800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1600</v>
-      </c>
-      <c r="W58" s="3">
-        <v>51600</v>
       </c>
       <c r="X58" s="3">
         <v>51600</v>
       </c>
       <c r="Y58" s="3">
+        <v>51600</v>
+      </c>
+      <c r="Z58" s="3">
         <v>51500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>51300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1000</v>
-      </c>
-      <c r="AB58" s="3">
-        <v>1100</v>
       </c>
       <c r="AC58" s="3">
         <v>1100</v>
       </c>
       <c r="AD58" s="3">
-        <v>600</v>
+        <v>1100</v>
       </c>
       <c r="AE58" s="3">
         <v>600</v>
       </c>
       <c r="AF58" s="3">
+        <v>600</v>
+      </c>
+      <c r="AG58" s="3">
         <v>150300</v>
       </c>
-      <c r="AG58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH58" s="3" t="s">
         <v>5</v>
       </c>
@@ -5576,101 +5710,104 @@
       <c r="AK58" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL58" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>409400</v>
+      </c>
+      <c r="E59" s="3">
         <v>372700</v>
       </c>
-      <c r="E59" s="3">
-        <v>351400</v>
-      </c>
       <c r="F59" s="3">
+        <v>631800</v>
+      </c>
+      <c r="G59" s="3">
         <v>354900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>333800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>305200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>604700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>305400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>299100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>285300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>562200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>298900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>306900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>239900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>904900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>946900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>902400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>850100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>832700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>870300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>834100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>839900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>910300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>986900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>920100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>914900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>926700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>929100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>881500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>834900</v>
       </c>
-      <c r="AG59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH59" s="3" t="s">
         <v>5</v>
       </c>
@@ -5683,101 +5820,104 @@
       <c r="AK59" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL59" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1637100</v>
+      </c>
+      <c r="E60" s="3">
         <v>1479500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1531700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1588000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1607800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1865500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1915600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1649600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1426900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1353700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1410900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1394100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1294900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1140100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1108100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1149500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1098800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1008900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1030800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1060700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1077400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1110700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1187400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1246600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1131000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1151300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1144400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1156300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1109800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1188900</v>
       </c>
-      <c r="AG60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH60" s="3" t="s">
         <v>5</v>
       </c>
@@ -5790,101 +5930,104 @@
       <c r="AK60" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL60" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1600500</v>
+      </c>
+      <c r="E61" s="3">
         <v>1639000</v>
       </c>
-      <c r="E61" s="3">
-        <v>1331900</v>
-      </c>
       <c r="F61" s="3">
+        <v>1337100</v>
+      </c>
+      <c r="G61" s="3">
         <v>1340200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1342100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>900000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>904900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1236900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1351100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1358700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>868600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>943800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>877400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>854400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>745900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>696800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>795100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>594500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>594300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>593100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>592500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>592100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>541700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>538400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>250100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>315300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>250600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>250000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>250100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>510000</v>
       </c>
-      <c r="AG61" s="3">
-        <v>0</v>
-      </c>
       <c r="AH61" s="3">
         <v>0</v>
       </c>
@@ -5897,101 +6040,104 @@
       <c r="AK61" s="3">
         <v>0</v>
       </c>
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>111500</v>
+      </c>
+      <c r="E62" s="3">
         <v>127500</v>
       </c>
-      <c r="E62" s="3">
-        <v>126200</v>
-      </c>
       <c r="F62" s="3">
+        <v>120900</v>
+      </c>
+      <c r="G62" s="3">
         <v>126300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>130400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>126700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>121900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>114600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>131200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>133100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>138100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>126500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>124400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>123200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>248200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>243600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>251300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>254800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>268700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>316300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>318900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>321800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>347100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>364400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>363800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>354600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>394700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>361900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>357600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>329400</v>
       </c>
-      <c r="AG62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH62" s="3" t="s">
         <v>5</v>
       </c>
@@ -6004,8 +6150,11 @@
       <c r="AK62" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL62" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6111,8 +6260,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6218,8 +6370,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6325,101 +6480,104 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3359200</v>
+      </c>
+      <c r="E66" s="3">
         <v>3258000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3001900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3072100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3099600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2903400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2953500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3028900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2919100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2855300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2427300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2484900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2316700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2130300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2154600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2141900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2181600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1890700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1930200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1999900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2025800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2068200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2123900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2191300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1783600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1853300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1820500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1796300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1754800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2060100</v>
       </c>
-      <c r="AG66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH66" s="3" t="s">
         <v>5</v>
       </c>
@@ -6432,8 +6590,11 @@
       <c r="AK66" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL66" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6471,8 +6632,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6578,8 +6740,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6685,8 +6850,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6792,8 +6960,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6899,101 +7070,104 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>694500</v>
+      </c>
+      <c r="E72" s="3">
         <v>709700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>661200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>605800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>542000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>487600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>426800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>227300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>155500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>87300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>203700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>158900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>111500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>68400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>43100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>15000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-14600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-32900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-53500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-82700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-102000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-108700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-120600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-142100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-182800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-206100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-218000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-64900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-424900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>75800</v>
       </c>
-      <c r="AG72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH72" s="3" t="s">
         <v>5</v>
       </c>
@@ -7006,8 +7180,11 @@
       <c r="AK72" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL72" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7113,8 +7290,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7220,8 +7400,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7327,101 +7510,104 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2631400</v>
+      </c>
+      <c r="E76" s="3">
         <v>2649600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2642000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2557800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2515900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2453800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2416400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2312500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2218500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2149700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2287200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2172700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2119400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2063900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2043600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1953100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1928200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1918200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1900800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1824100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1813500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1796800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1813800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1727500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1667500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1635300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1629900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1566400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1500600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>972900</v>
       </c>
-      <c r="AG76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH76" s="3" t="s">
         <v>5</v>
       </c>
@@ -7434,8 +7620,11 @@
       <c r="AK76" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL76" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7541,227 +7730,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43371</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43280</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43189</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43098</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="E81" s="3">
         <v>52900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>55600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>64100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>55200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>66200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>54200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>72000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>69200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>39800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>44900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>47400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>43200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>25600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>28100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>29600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>18300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>20700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>29000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>19400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>6700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>9000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>21600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>40700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>23300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>13000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>13700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>56800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>40300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>9700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>7400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>41200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>148400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>25300</v>
       </c>
-      <c r="AK81" s="3" t="s">
+      <c r="AL81" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7799,115 +7997,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E83" s="3">
         <v>11000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>10900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>11200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>10600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>10800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>11100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>11400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>10600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>10400</v>
-      </c>
-      <c r="M83" s="3">
-        <v>10500</v>
       </c>
       <c r="N83" s="3">
         <v>10500</v>
       </c>
       <c r="O83" s="3">
+        <v>10500</v>
+      </c>
+      <c r="P83" s="3">
         <v>10900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>10400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>29800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>29600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>30600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>30500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>37700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>37200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>34600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>34700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>32500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>31000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>32100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>32400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>33000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>31000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>31100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>30600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>23200</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>23600</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>14000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>9000</v>
       </c>
-      <c r="AK83" s="3" t="s">
+      <c r="AL83" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8013,8 +8215,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8120,8 +8325,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8227,8 +8435,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8334,8 +8545,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8441,115 +8655,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>57600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>167500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>162900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>159800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-11800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>126800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>299000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>161200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-63400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>190100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>203600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>23000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>89200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>123000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>51100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-25700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>89900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>77300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>104400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-66000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>175700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>144900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>87500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-119000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>89600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>179100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>11600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-60100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>184800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>108300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>57000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-65400</v>
       </c>
-      <c r="AK89" s="3" t="s">
+      <c r="AL89" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8587,115 +8807,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-16100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-14900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-31900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-13100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-9400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-13500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-18800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-11700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-9300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-9400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-9500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-12900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-9800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-10800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-6200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-9100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-8300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-3600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-4700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-4400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-4900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-6200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-10300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-12600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-23600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-18100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-14900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-11000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-9800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-8900</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-5400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-5200</v>
       </c>
-      <c r="AK91" s="3" t="s">
+      <c r="AL91" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8801,8 +9025,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8908,115 +9135,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-21900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-364600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-67300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-24000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-102600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-61700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-212100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-255900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-43200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-45500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-48700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-243000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-63500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-20800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-14800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>1200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-390400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-13400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-10400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-210600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-8800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-310300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-10300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-13600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-12200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-29100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-229500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-11100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-301100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-7800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-487600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-8200</v>
       </c>
-      <c r="AK94" s="3" t="s">
+      <c r="AL94" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9054,8 +9287,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9098,8 +9332,8 @@
       <c r="P96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -9161,8 +9395,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9268,8 +9505,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9375,8 +9615,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9482,325 +9725,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-53100</v>
+      </c>
+      <c r="E100" s="3">
         <v>186500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-57600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-127300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>81700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-110900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-15200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-13100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-12400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>259500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-74300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>66600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-12500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>40200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-102300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>180900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-18400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-10800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-73400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-11000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-11200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>3100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>345900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-64600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>63700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-11300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-14200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>80900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>210600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-117700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-64800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>231800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>6100</v>
       </c>
-      <c r="AK100" s="3" t="s">
+      <c r="AL100" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E101" s="3">
         <v>500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-4700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-1300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-1400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-1400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-1100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>600</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-300</v>
-      </c>
-      <c r="AD101" s="3">
-        <v>-400</v>
       </c>
       <c r="AE101" s="3">
         <v>-400</v>
       </c>
       <c r="AF101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AG101" s="3">
         <v>-200</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-500</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-600</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>200</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-800</v>
       </c>
-      <c r="AK101" s="3" t="s">
+      <c r="AL101" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-17900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-182500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>43800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>11200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>141600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-183800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-105300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>30400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>105300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>150200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>67500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>26800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-41900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-42100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>115000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>20700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-159900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-57100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>67200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-207900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>85200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-87800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-130500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>481100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>9900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-68700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>48900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-64900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>80900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-150700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>67000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>35100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-198700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-68300</v>
       </c>
-      <c r="AK102" s="3" t="s">
+      <c r="AL102" s="3" t="s">
         <v>5</v>
       </c>
     </row>
